--- a/docs/PIMS_DASHBOARD_System_Specification_KR.xlsx
+++ b/docs/PIMS_DASHBOARD_System_Specification_KR.xlsx
@@ -6,13 +6,14 @@
   <sheets>
     <sheet sheetId="1" name="데이터 연동 명세서" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="입력방식별 분류 요약" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="지표 연동 매트릭스" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="248">
   <si>
     <t>PIMS-DASHBOARD 시스템 지표별 데이터 연동 및 입력 출처 명세서</t>
   </si>
@@ -540,13 +541,229 @@
   </si>
   <si>
     <t>기준 환율(USD/VND/KRW), 프로젝트 일반제원(규모, 발주처, 연면적, 계약조건), 공종별 원가 투입 계획, 월간 계획 공정률(%), 입찰(Bidding) 원가율, 경영 실적/전망 코멘트.</t>
+  </si>
+  <si>
+    <t>지표 및 데이터 연동(Lineage) 매핑 매트릭스</t>
+  </si>
+  <si>
+    <t>화면</t>
+  </si>
+  <si>
+    <t>지표명</t>
+  </si>
+  <si>
+    <t>입력 유형</t>
+  </si>
+  <si>
+    <t>PIMSVINA 메뉴</t>
+  </si>
+  <si>
+    <t>PIMSVINA 명칭 UI</t>
+  </si>
+  <si>
+    <t>전체 관리 대시보드 - 종합 현황</t>
+  </si>
+  <si>
+    <t>엑셀 업로드</t>
+  </si>
+  <si>
+    <t>Monthly Management Performance Registration</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Revenue line cumulative)</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Operating Profit line cumulative)</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Full-Year Total)</t>
+  </si>
+  <si>
+    <t>전체 관리 대시보드 - 차트 영역</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Monthly Revenue)</t>
+  </si>
+  <si>
+    <t>Management Report Excel (P&amp;L lines)</t>
+  </si>
+  <si>
+    <t>Management Report Excel (Orders/Contracts)</t>
+  </si>
+  <si>
+    <t>1. Site Fund Movement (Cash / Bank) / Cash Flow Sheet</t>
+  </si>
+  <si>
+    <t>Cash Flow Excel Upload</t>
+  </si>
+  <si>
+    <t>전체 관리 대시보드 - 표 및 요약</t>
+  </si>
+  <si>
+    <t>경영실적 현황 표</t>
+  </si>
+  <si>
+    <t>Management Report Excel Sheet</t>
+  </si>
+  <si>
+    <t>전체 관리 대시보드 - 코멘트</t>
+  </si>
+  <si>
+    <t>수기 직접입력</t>
+  </si>
+  <si>
+    <t>N/A (Dashboard Exclusive)</t>
+  </si>
+  <si>
+    <t>Bottom Comment Panel (Edit &amp; Save)</t>
+  </si>
+  <si>
+    <t>시공 프로젝트 상세 - 개요 탭</t>
+  </si>
+  <si>
+    <t>ERP 자동동기화</t>
+  </si>
+  <si>
+    <t>Construction Overview Registration / Contract Summary</t>
+  </si>
+  <si>
+    <t>Total Contract Won Amount (TOTALCTRTWONAMT)</t>
+  </si>
+  <si>
+    <t>Construction Overview Registration &gt; Period</t>
+  </si>
+  <si>
+    <t>Actual Start (STCONSTDATE) ~ Sched. Completion (CMPLSCHDDATE)</t>
+  </si>
+  <si>
+    <t>Construction Overview Registration (Unregistered items)</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; 0. Overview Information</t>
+  </si>
+  <si>
+    <t>Construction Overview Registration &gt; Aerial View</t>
+  </si>
+  <si>
+    <t>Aerial View Picture File (AIRVIEWPICPATH)</t>
+  </si>
+  <si>
+    <t>시공 프로젝트 상세 - 공정 탭</t>
+  </si>
+  <si>
+    <t>Cost Progress Rate (%) / Execution Progress (Site)</t>
+  </si>
+  <si>
+    <t>Calculated progress rate based on monthly cost input</t>
+  </si>
+  <si>
+    <t>N/A (Site Schedule Table)</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; 1. Monthly Progress / 2. Milestones (Excel Upload supported)</t>
+  </si>
+  <si>
+    <t>Monthly Construction Photo Registration</t>
+  </si>
+  <si>
+    <t>Monthly Photo List with Location/Trade Notes</t>
+  </si>
+  <si>
+    <t>시공 프로젝트 상세 - 매출/원가 탭</t>
+  </si>
+  <si>
+    <t>Monthly Management Performance Registration / Excel</t>
+  </si>
+  <si>
+    <t>Site Monthly Revenue Column</t>
+  </si>
+  <si>
+    <t>원가율 설정 (입찰, 실행예산, 준공추정)</t>
+  </si>
+  <si>
+    <t>Execution Budget Proposal / Settlement Cost Ratio</t>
+  </si>
+  <si>
+    <t>Business Budget, Contract Amount, Gross Profit Ratio</t>
+  </si>
+  <si>
+    <t>시공 프로젝트 상세 - 외주 탭</t>
+  </si>
+  <si>
+    <t>Execution Progress (Site) / Sub-Contract Detailed Bid / Resolution</t>
+  </si>
+  <si>
+    <t>Budget (A), Executed Budget, Resolved (B), Current Month, Cumulative (C), Exec Rate</t>
+  </si>
+  <si>
+    <t>시공 프로젝트 상세 - 비용 탭</t>
+  </si>
+  <si>
+    <t>비목별(CBS) 예산 집행 현황 (직접비, 간접비, 예비비)</t>
+  </si>
+  <si>
+    <t>Execution Budget Proposal &gt; Cost Breakdown</t>
+  </si>
+  <si>
+    <t>Budget &amp; Incurred Cost by Standard CBS</t>
+  </si>
+  <si>
+    <t>N/A (Site Cost Incurrence Plan)</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; 4. Cost Plan/Actual by Work Type</t>
+  </si>
+  <si>
+    <t>시공 프로젝트 상세 - 자금수지 탭</t>
+  </si>
+  <si>
+    <t>1. Site Fund Movement (Cash / Bank) / Transactions</t>
+  </si>
+  <si>
+    <t>Income / Withdrawal / Opening Balance</t>
+  </si>
+  <si>
+    <t>용역 프로젝트 상세 - 개요 및 매출</t>
+  </si>
+  <si>
+    <t>Service Contract / Order Management</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; Service Overview (Period, Client, Scope, Payment Terms)</t>
+  </si>
+  <si>
+    <t>용역 프로젝트 상세 - 매출 및 원가 탭</t>
+  </si>
+  <si>
+    <t>Monthly Management Performance / Service Cost</t>
+  </si>
+  <si>
+    <t>Data Entry Tab &gt; 3. Monthly Cost of Revenue</t>
+  </si>
+  <si>
+    <t>시스템 관리 - 데이터 연동 및 업로드</t>
+  </si>
+  <si>
+    <t>Contract Exchange Rate / CHTB_EXCHANGE_RATIO</t>
+  </si>
+  <si>
+    <t>Dashboard Top FX Rate Editor Modal</t>
+  </si>
+  <si>
+    <t>Upload Modal (Management Report Excel Parsing)</t>
+  </si>
+  <si>
+    <t>ERP All Modules</t>
+  </si>
+  <si>
+    <t>Top 'PIMS Sync' button -&gt; Preview Popup -&gt; Confirm Apply</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -567,29 +784,40 @@
       <name val="Malgun Gothic"/>
     </font>
     <font>
-      <sz val="9.5"/>
+      <sz val="9"/>
       <name val="Malgun Gothic"/>
     </font>
     <font>
       <b/>
       <color rgb="2A4365"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
       <name val="Malgun Gothic"/>
     </font>
     <font>
       <b/>
       <color rgb="744210"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
       <name val="Malgun Gothic"/>
     </font>
     <font>
       <b/>
       <color rgb="234E52"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
       <name val="Malgun Gothic"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1A365D"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -621,8 +849,13 @@
         <fgColor rgb="E6FFFA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF8FF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -660,11 +893,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -686,6 +934,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1810,7 +2067,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1894,6 +2151,528 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>